--- a/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-5/04-test-cases/CYC-5-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-5/04-test-cases/CYC-5-test-cases.xlsx
@@ -953,7 +953,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:20.925Z</t>
+    <t>2026-10-02T04:13:59.711Z</t>
   </si>
   <si>
     <t>Column order</t>
